--- a/output/pdf_financials_xlsx/OROG.xlsx
+++ b/output/pdf_financials_xlsx/OROG.xlsx
@@ -1131,13 +1131,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.548563</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.406972</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.265463</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.548563</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.406972</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.265463</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.406972</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.265463</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">

--- a/output/pdf_financials_xlsx/OROG.xlsx
+++ b/output/pdf_financials_xlsx/OROG.xlsx
@@ -2469,10 +2469,10 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003174</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004811</v>
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
@@ -4216,7 +4216,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
